--- a/reports/빅딜/history/2026-05-18/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-05-18/빅딜_training_mgf_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">밀크런!$A$1:$J$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">블랙소울!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">비련!$A$1:$J$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">빅딜!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">초코나라!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">털미녀!$A$1:$J$28</definedName>
   </definedNames>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="710">
   <si>
     <t>guild_name</t>
   </si>
@@ -1230,6 +1230,9 @@
     <t>3408억 5041만</t>
   </si>
   <si>
+    <t>1위</t>
+  </si>
+  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -1239,6 +1242,9 @@
     <t>127조 4158억 2520만</t>
   </si>
   <si>
+    <t>2위</t>
+  </si>
+  <si>
     <t>울힝</t>
   </si>
   <si>
@@ -1248,6 +1254,9 @@
     <t>124조 2857억 5103만</t>
   </si>
   <si>
+    <t>3위</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
@@ -1281,6 +1290,9 @@
     <t>37조 2025억 1259만</t>
   </si>
   <si>
+    <t>7위</t>
+  </si>
+  <si>
     <t>익맹</t>
   </si>
   <si>
@@ -1290,6 +1302,9 @@
     <t>29조 2855억 7714만</t>
   </si>
   <si>
+    <t>8위</t>
+  </si>
+  <si>
     <t>단풍카우</t>
   </si>
   <si>
@@ -1311,6 +1326,9 @@
     <t>18조 6811억 3690만</t>
   </si>
   <si>
+    <t>10위</t>
+  </si>
+  <si>
     <t>아르미느</t>
   </si>
   <si>
@@ -1320,6 +1338,9 @@
     <t>18조 611억 3324만</t>
   </si>
   <si>
+    <t>11위</t>
+  </si>
+  <si>
     <t>양정팔</t>
   </si>
   <si>
@@ -1329,6 +1350,9 @@
     <t>18조 33억 1513만</t>
   </si>
   <si>
+    <t>12위</t>
+  </si>
+  <si>
     <t>굴러가는일상</t>
   </si>
   <si>
@@ -1338,6 +1362,9 @@
     <t>17조 2503억 3903만</t>
   </si>
   <si>
+    <t>13위</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
@@ -1347,6 +1374,9 @@
     <t>14조 4786억 4858만</t>
   </si>
   <si>
+    <t>14위</t>
+  </si>
+  <si>
     <t>KR#TAKIN9CP37</t>
   </si>
   <si>
@@ -1356,6 +1386,9 @@
     <t>12조 9889억 8160만</t>
   </si>
   <si>
+    <t>15위</t>
+  </si>
+  <si>
     <t>흑두부</t>
   </si>
   <si>
@@ -1365,6 +1398,9 @@
     <t>12조 4350억 5906만</t>
   </si>
   <si>
+    <t>16위</t>
+  </si>
+  <si>
     <t>우후</t>
   </si>
   <si>
@@ -1374,6 +1410,9 @@
     <t>12조 3713억 1192만</t>
   </si>
   <si>
+    <t>17위</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
@@ -1383,6 +1422,9 @@
     <t>10조 1633억 6981만</t>
   </si>
   <si>
+    <t>18위</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -1392,6 +1434,9 @@
     <t>9조 8104억 260만</t>
   </si>
   <si>
+    <t>19위</t>
+  </si>
+  <si>
     <t>꾸르꾸르</t>
   </si>
   <si>
@@ -1401,6 +1446,21 @@
     <t>8조 6441억 726만</t>
   </si>
   <si>
+    <t>20위</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>7조 9942억 9967만</t>
+  </si>
+  <si>
+    <t>21위</t>
+  </si>
+  <si>
     <t>므고</t>
   </si>
   <si>
@@ -1410,6 +1470,9 @@
     <t>7조 9273억 406만</t>
   </si>
   <si>
+    <t>22위</t>
+  </si>
+  <si>
     <t>민들레꽃</t>
   </si>
   <si>
@@ -1419,6 +1482,9 @@
     <t>6조 8368억 7385만</t>
   </si>
   <si>
+    <t>23위</t>
+  </si>
+  <si>
     <t>불보독지</t>
   </si>
   <si>
@@ -1428,6 +1494,21 @@
     <t>6조 2311억 5403만</t>
   </si>
   <si>
+    <t>24위</t>
+  </si>
+  <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>5조 3996억 7064만</t>
+  </si>
+  <si>
+    <t>25위</t>
+  </si>
+  <si>
     <t>플로우00</t>
   </si>
   <si>
@@ -1437,6 +1518,9 @@
     <t>4조 9551억 9411만</t>
   </si>
   <si>
+    <t>26위</t>
+  </si>
+  <si>
     <t>제스프리</t>
   </si>
   <si>
@@ -1446,6 +1530,9 @@
     <t>4조 3416억 2655만</t>
   </si>
   <si>
+    <t>27위</t>
+  </si>
+  <si>
     <t>데드캣</t>
   </si>
   <si>
@@ -1453,6 +1540,30 @@
   </si>
   <si>
     <t>3조 4048억 3962만</t>
+  </si>
+  <si>
+    <t>28위</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>3조 3267억 9445만</t>
+  </si>
+  <si>
+    <t>29위</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>2조 8773억 332만</t>
   </si>
   <si>
     <t>량용</t>
@@ -5904,7 +6015,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5953,16 +6064,16 @@
         <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>81</v>
+        <v>399</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -5974,7 +6085,7 @@
         <v>112</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -5985,16 +6096,16 @@
         <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>403</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -6006,7 +6117,7 @@
         <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -6017,7 +6128,7 @@
         <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>407</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>49</v>
@@ -6026,7 +6137,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>173</v>
@@ -6038,7 +6149,7 @@
         <v>98</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -6049,16 +6160,16 @@
         <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -6070,7 +6181,7 @@
         <v>127</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -6081,16 +6192,16 @@
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -6102,7 +6213,7 @@
         <v>98</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -6113,16 +6224,16 @@
         <v>41</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -6134,7 +6245,7 @@
         <v>117</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -6145,16 +6256,16 @@
         <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>419</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -6166,7 +6277,7 @@
         <v>165</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -6177,16 +6288,16 @@
         <v>41</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>119</v>
+        <v>423</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -6198,7 +6309,7 @@
         <v>112</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -6209,28 +6320,28 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>127</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -6241,16 +6352,16 @@
         <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>129</v>
+        <v>431</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -6262,7 +6373,7 @@
         <v>117</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -6273,16 +6384,16 @@
         <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>134</v>
+        <v>435</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -6294,7 +6405,7 @@
         <v>117</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -6305,16 +6416,16 @@
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>138</v>
+        <v>439</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -6326,7 +6437,7 @@
         <v>117</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -6337,16 +6448,16 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>142</v>
+        <v>443</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -6358,7 +6469,7 @@
         <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -6369,16 +6480,16 @@
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>146</v>
+        <v>447</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -6390,7 +6501,7 @@
         <v>165</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -6401,16 +6512,16 @@
         <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>150</v>
+        <v>451</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -6422,7 +6533,7 @@
         <v>165</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>23</v>
@@ -6433,16 +6544,16 @@
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>154</v>
+        <v>455</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -6454,7 +6565,7 @@
         <v>186</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
@@ -6465,16 +6576,16 @@
         <v>41</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>459</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -6486,7 +6597,7 @@
         <v>186</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>23</v>
@@ -6497,16 +6608,16 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>162</v>
+        <v>463</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -6518,7 +6629,7 @@
         <v>186</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
@@ -6529,16 +6640,16 @@
         <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>167</v>
+        <v>467</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>453</v>
+        <v>468</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>454</v>
+        <v>469</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -6550,7 +6661,7 @@
         <v>186</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>455</v>
+        <v>470</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>23</v>
@@ -6561,28 +6672,28 @@
         <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>471</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>457</v>
+        <v>473</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>132</v>
+        <v>196</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>458</v>
+        <v>474</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>23</v>
@@ -6593,28 +6704,28 @@
         <v>41</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>175</v>
+        <v>475</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>196</v>
+        <v>132</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>23</v>
@@ -6625,28 +6736,28 @@
         <v>41</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>179</v>
+        <v>479</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>23</v>
@@ -6657,28 +6768,28 @@
         <v>41</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>183</v>
+        <v>483</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>424</v>
+        <v>191</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>23</v>
@@ -6689,28 +6800,28 @@
         <v>41</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>188</v>
+        <v>487</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>217</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>23</v>
@@ -6721,35 +6832,163 @@
         <v>41</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>193</v>
+        <v>491</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>471</v>
+        <v>492</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>472</v>
+        <v>493</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>122</v>
+        <v>429</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>473</v>
+        <v>494</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6776,6 +7015,10 @@
     <hyperlink ref="E24" r:id="rId23"/>
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6836,13 +7079,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -6854,7 +7097,7 @@
         <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -6868,13 +7111,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -6886,7 +7129,7 @@
         <v>98</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -6900,13 +7143,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -6918,7 +7161,7 @@
         <v>112</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -6932,13 +7175,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -6950,7 +7193,7 @@
         <v>117</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -6970,7 +7213,7 @@
         <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>173</v>
@@ -6982,7 +7225,7 @@
         <v>112</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -6996,25 +7239,25 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>117</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -7028,13 +7271,13 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -7046,7 +7289,7 @@
         <v>117</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -7060,13 +7303,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -7078,7 +7321,7 @@
         <v>165</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -7092,13 +7335,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -7110,7 +7353,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -7124,13 +7367,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>501</v>
+        <v>538</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -7142,7 +7385,7 @@
         <v>117</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -7156,13 +7399,13 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -7174,7 +7417,7 @@
         <v>117</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -7188,13 +7431,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>506</v>
+        <v>543</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>506</v>
+        <v>543</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -7206,7 +7449,7 @@
         <v>186</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>508</v>
+        <v>545</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -7220,13 +7463,13 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>510</v>
+        <v>547</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -7238,7 +7481,7 @@
         <v>186</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -7252,13 +7495,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>513</v>
+        <v>550</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -7270,7 +7513,7 @@
         <v>217</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -7284,13 +7527,13 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -7302,7 +7545,7 @@
         <v>186</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>23</v>
@@ -7316,13 +7559,13 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -7334,7 +7577,7 @@
         <v>165</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
@@ -7348,13 +7591,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -7366,7 +7609,7 @@
         <v>186</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>23</v>
@@ -7380,13 +7623,13 @@
         <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>84</v>
@@ -7398,7 +7641,7 @@
         <v>186</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
@@ -7412,13 +7655,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -7430,7 +7673,7 @@
         <v>217</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>23</v>
@@ -7444,13 +7687,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -7462,7 +7705,7 @@
         <v>217</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>23</v>
@@ -7476,13 +7719,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -7494,7 +7737,7 @@
         <v>217</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>23</v>
@@ -7508,13 +7751,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -7526,7 +7769,7 @@
         <v>217</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>23</v>
@@ -7617,13 +7860,13 @@
         <v>81</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>84</v>
@@ -7635,7 +7878,7 @@
         <v>309</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -7649,13 +7892,13 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>542</v>
+        <v>579</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>543</v>
+        <v>580</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
@@ -7667,7 +7910,7 @@
         <v>165</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>544</v>
+        <v>581</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -7681,13 +7924,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>546</v>
+        <v>583</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -7699,7 +7942,7 @@
         <v>186</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -7713,25 +7956,25 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -7745,13 +7988,13 @@
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -7763,7 +8006,7 @@
         <v>165</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -7777,25 +8020,25 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -7809,13 +8052,13 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>559</v>
+        <v>596</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -7827,7 +8070,7 @@
         <v>186</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -7841,13 +8084,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>561</v>
+        <v>598</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>561</v>
+        <v>598</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>562</v>
+        <v>599</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -7859,7 +8102,7 @@
         <v>186</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -7873,13 +8116,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>564</v>
+        <v>601</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>564</v>
+        <v>601</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>565</v>
+        <v>602</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -7891,7 +8134,7 @@
         <v>186</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -7905,13 +8148,13 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>567</v>
+        <v>604</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>567</v>
+        <v>604</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
@@ -7923,7 +8166,7 @@
         <v>165</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -7937,13 +8180,13 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>570</v>
+        <v>607</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>570</v>
+        <v>607</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>571</v>
+        <v>608</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -7955,7 +8198,7 @@
         <v>186</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -7969,13 +8212,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>573</v>
+        <v>610</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>574</v>
+        <v>611</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -7987,7 +8230,7 @@
         <v>186</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -8001,13 +8244,13 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>576</v>
+        <v>613</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>576</v>
+        <v>613</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>577</v>
+        <v>614</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -8019,7 +8262,7 @@
         <v>186</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>578</v>
+        <v>615</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -8033,13 +8276,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>579</v>
+        <v>616</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>579</v>
+        <v>616</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>580</v>
+        <v>617</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -8051,7 +8294,7 @@
         <v>186</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -8065,13 +8308,13 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
@@ -8083,7 +8326,7 @@
         <v>186</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>23</v>
@@ -8097,13 +8340,13 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>585</v>
+        <v>622</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
@@ -8115,7 +8358,7 @@
         <v>217</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
@@ -8129,13 +8372,13 @@
         <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>588</v>
+        <v>625</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>589</v>
+        <v>626</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>84</v>
@@ -8147,7 +8390,7 @@
         <v>217</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>590</v>
+        <v>627</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>23</v>
@@ -8167,7 +8410,7 @@
         <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>591</v>
+        <v>628</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>173</v>
@@ -8179,7 +8422,7 @@
         <v>186</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
@@ -8193,13 +8436,13 @@
         <v>167</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>594</v>
+        <v>631</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>84</v>
@@ -8211,7 +8454,7 @@
         <v>186</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>595</v>
+        <v>632</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>23</v>
@@ -8225,13 +8468,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>596</v>
+        <v>633</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>596</v>
+        <v>633</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>597</v>
+        <v>634</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>84</v>
@@ -8243,7 +8486,7 @@
         <v>217</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>598</v>
+        <v>635</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>23</v>
@@ -8257,13 +8500,13 @@
         <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>600</v>
+        <v>637</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>84</v>
@@ -8275,7 +8518,7 @@
         <v>217</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>601</v>
+        <v>638</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>23</v>
@@ -8289,13 +8532,13 @@
         <v>179</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>84</v>
@@ -8307,7 +8550,7 @@
         <v>217</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>604</v>
+        <v>641</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>23</v>
@@ -8321,13 +8564,13 @@
         <v>183</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>605</v>
+        <v>642</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>606</v>
+        <v>643</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>84</v>
@@ -8339,7 +8582,7 @@
         <v>217</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>607</v>
+        <v>644</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>23</v>
@@ -8353,25 +8596,25 @@
         <v>188</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>608</v>
+        <v>645</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>608</v>
+        <v>645</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>609</v>
+        <v>646</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>23</v>
@@ -8385,13 +8628,13 @@
         <v>193</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>84</v>
@@ -8403,7 +8646,7 @@
         <v>217</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>614</v>
+        <v>651</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>23</v>
@@ -8417,13 +8660,13 @@
         <v>198</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>615</v>
+        <v>652</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>615</v>
+        <v>652</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>616</v>
+        <v>653</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>84</v>
@@ -8435,7 +8678,7 @@
         <v>217</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>23</v>
@@ -8449,13 +8692,13 @@
         <v>202</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>618</v>
+        <v>655</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>619</v>
+        <v>656</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>84</v>
@@ -8464,10 +8707,10 @@
         <v>132</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>620</v>
+        <v>657</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>23</v>
@@ -8569,7 +8812,7 @@
         <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>621</v>
+        <v>658</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>173</v>
@@ -8581,7 +8824,7 @@
         <v>117</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>622</v>
+        <v>659</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>23</v>
@@ -8595,25 +8838,25 @@
         <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>624</v>
+        <v>661</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>186</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>625</v>
+        <v>662</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>23</v>
@@ -8627,13 +8870,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>626</v>
+        <v>663</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>626</v>
+        <v>663</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>84</v>
@@ -8645,7 +8888,7 @@
         <v>186</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>628</v>
+        <v>665</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>23</v>
@@ -8659,13 +8902,13 @@
         <v>100</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>630</v>
+        <v>667</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>84</v>
@@ -8677,7 +8920,7 @@
         <v>217</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>631</v>
+        <v>668</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>23</v>
@@ -8691,13 +8934,13 @@
         <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>632</v>
+        <v>669</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>632</v>
+        <v>669</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>84</v>
@@ -8709,7 +8952,7 @@
         <v>217</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>634</v>
+        <v>671</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>23</v>
@@ -8723,13 +8966,13 @@
         <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>636</v>
+        <v>673</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>84</v>
@@ -8741,7 +8984,7 @@
         <v>217</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>637</v>
+        <v>674</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
@@ -8755,13 +8998,13 @@
         <v>114</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>638</v>
+        <v>675</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>638</v>
+        <v>675</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>639</v>
+        <v>676</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>84</v>
@@ -8770,10 +9013,10 @@
         <v>196</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>641</v>
+        <v>678</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>23</v>
@@ -8787,13 +9030,13 @@
         <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>642</v>
+        <v>679</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>642</v>
+        <v>679</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>643</v>
+        <v>680</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>84</v>
@@ -8802,10 +9045,10 @@
         <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>644</v>
+        <v>681</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>23</v>
@@ -8819,13 +9062,13 @@
         <v>124</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>645</v>
+        <v>682</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>645</v>
+        <v>682</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>84</v>
@@ -8834,10 +9077,10 @@
         <v>191</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>23</v>
@@ -8851,25 +9094,25 @@
         <v>129</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
@@ -8883,13 +9126,13 @@
         <v>134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>652</v>
+        <v>689</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>84</v>
@@ -8901,7 +9144,7 @@
         <v>217</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>653</v>
+        <v>690</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -8915,13 +9158,13 @@
         <v>138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>655</v>
+        <v>692</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>84</v>
@@ -8930,10 +9173,10 @@
         <v>122</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>656</v>
+        <v>693</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>23</v>
@@ -8947,13 +9190,13 @@
         <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>657</v>
+        <v>694</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>657</v>
+        <v>694</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>84</v>
@@ -8962,10 +9205,10 @@
         <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>610</v>
+        <v>647</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>23</v>
@@ -8979,13 +9222,13 @@
         <v>146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>84</v>
@@ -8994,10 +9237,10 @@
         <v>196</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>23</v>
@@ -9011,25 +9254,25 @@
         <v>150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>664</v>
+        <v>701</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>666</v>
+        <v>703</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>23</v>
@@ -9043,25 +9286,25 @@
         <v>154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>23</v>
